--- a/artfynd/A 64127-2023 artfynd.xlsx
+++ b/artfynd/A 64127-2023 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120846241</v>
+        <v>120846277</v>
       </c>
       <c r="B10" t="n">
-        <v>91975</v>
+        <v>90707</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,38 +1503,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sandträsket, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784627</v>
+        <v>784361</v>
       </c>
       <c r="R10" t="n">
-        <v>7349780</v>
+        <v>7350179</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120846277</v>
+        <v>120846241</v>
       </c>
       <c r="B11" t="n">
-        <v>90707</v>
+        <v>91975</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,38 +1605,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsket, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784361</v>
+        <v>784627</v>
       </c>
       <c r="R11" t="n">
-        <v>7350179</v>
+        <v>7349780</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>

--- a/artfynd/A 64127-2023 artfynd.xlsx
+++ b/artfynd/A 64127-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120846297</v>
       </c>
       <c r="B2" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120846289</v>
+        <v>120846281</v>
       </c>
       <c r="B3" t="n">
-        <v>91975</v>
+        <v>91973</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784312</v>
+        <v>784273</v>
       </c>
       <c r="R3" t="n">
-        <v>7350223</v>
+        <v>7350210</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120846283</v>
+        <v>120846287</v>
       </c>
       <c r="B4" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784262</v>
+        <v>784293</v>
       </c>
       <c r="R4" t="n">
-        <v>7350259</v>
+        <v>7350235</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120846276</v>
+        <v>120846275</v>
       </c>
       <c r="B5" t="n">
-        <v>57364</v>
+        <v>91599</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4745</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784412</v>
+        <v>784456</v>
       </c>
       <c r="R5" t="n">
-        <v>7350117</v>
+        <v>7350102</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120846284</v>
+        <v>120846280</v>
       </c>
       <c r="B6" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784257</v>
+        <v>784294</v>
       </c>
       <c r="R6" t="n">
-        <v>7350260</v>
+        <v>7350178</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120846291</v>
+        <v>120846279</v>
       </c>
       <c r="B7" t="n">
-        <v>91955</v>
+        <v>91973</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784307</v>
+        <v>784322</v>
       </c>
       <c r="R7" t="n">
-        <v>7350222</v>
+        <v>7350175</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120846281</v>
+        <v>120846284</v>
       </c>
       <c r="B8" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>784273</v>
+        <v>784257</v>
       </c>
       <c r="R8" t="n">
-        <v>7350210</v>
+        <v>7350260</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120846282</v>
+        <v>120846244</v>
       </c>
       <c r="B9" t="n">
-        <v>91991</v>
+        <v>57504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsket, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>784268</v>
+        <v>784470</v>
       </c>
       <c r="R9" t="n">
-        <v>7350210</v>
+        <v>7349932</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1494,7 +1494,7 @@
         <v>120846277</v>
       </c>
       <c r="B10" t="n">
-        <v>90707</v>
+        <v>90717</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120846241</v>
+        <v>120846292</v>
       </c>
       <c r="B11" t="n">
-        <v>91975</v>
+        <v>91967</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,38 +1605,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sandträsket, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784627</v>
+        <v>784322</v>
       </c>
       <c r="R11" t="n">
-        <v>7349780</v>
+        <v>7350217</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120846290</v>
+        <v>120846272</v>
       </c>
       <c r="B12" t="n">
-        <v>91963</v>
+        <v>98081</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,38 +1707,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsket, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784308</v>
+        <v>784454</v>
       </c>
       <c r="R12" t="n">
-        <v>7350215</v>
+        <v>7349938</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120846293</v>
+        <v>120846289</v>
       </c>
       <c r="B13" t="n">
-        <v>91963</v>
+        <v>91985</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>784365</v>
+        <v>784312</v>
       </c>
       <c r="R13" t="n">
-        <v>7350253</v>
+        <v>7350223</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120846288</v>
+        <v>120846286</v>
       </c>
       <c r="B14" t="n">
-        <v>91957</v>
+        <v>91973</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>784286</v>
+        <v>784290</v>
       </c>
       <c r="R14" t="n">
-        <v>7350227</v>
+        <v>7350243</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120846286</v>
+        <v>120846285</v>
       </c>
       <c r="B15" t="n">
-        <v>91963</v>
+        <v>92001</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>784290</v>
+        <v>784260</v>
       </c>
       <c r="R15" t="n">
-        <v>7350243</v>
+        <v>7350253</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120846272</v>
+        <v>120846242</v>
       </c>
       <c r="B16" t="n">
-        <v>98071</v>
+        <v>91985</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>784454</v>
+        <v>784572</v>
       </c>
       <c r="R16" t="n">
-        <v>7349938</v>
+        <v>7349815</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120846292</v>
+        <v>120846243</v>
       </c>
       <c r="B17" t="n">
-        <v>91957</v>
+        <v>98081</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,38 +2217,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsket, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>784322</v>
+        <v>784480</v>
       </c>
       <c r="R17" t="n">
-        <v>7350217</v>
+        <v>7349944</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120846279</v>
+        <v>120846291</v>
       </c>
       <c r="B18" t="n">
-        <v>91963</v>
+        <v>91965</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>784322</v>
+        <v>784307</v>
       </c>
       <c r="R18" t="n">
-        <v>7350175</v>
+        <v>7350222</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120846243</v>
+        <v>120846283</v>
       </c>
       <c r="B19" t="n">
-        <v>98071</v>
+        <v>91973</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,38 +2421,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sandträsket, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>784480</v>
+        <v>784262</v>
       </c>
       <c r="R19" t="n">
-        <v>7349944</v>
+        <v>7350259</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120846275</v>
+        <v>120846282</v>
       </c>
       <c r="B20" t="n">
-        <v>91589</v>
+        <v>92001</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>784456</v>
+        <v>784268</v>
       </c>
       <c r="R20" t="n">
-        <v>7350102</v>
+        <v>7350210</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120846244</v>
+        <v>120846241</v>
       </c>
       <c r="B21" t="n">
-        <v>57501</v>
+        <v>91985</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>784470</v>
+        <v>784627</v>
       </c>
       <c r="R21" t="n">
-        <v>7349932</v>
+        <v>7349780</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120846242</v>
+        <v>120846293</v>
       </c>
       <c r="B22" t="n">
-        <v>91975</v>
+        <v>91973</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,34 +2731,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sandträsket, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>784572</v>
+        <v>784365</v>
       </c>
       <c r="R22" t="n">
-        <v>7349815</v>
+        <v>7350253</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120846280</v>
+        <v>120846288</v>
       </c>
       <c r="B23" t="n">
-        <v>91963</v>
+        <v>91967</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2829,25 +2829,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>784294</v>
+        <v>784286</v>
       </c>
       <c r="R23" t="n">
-        <v>7350178</v>
+        <v>7350227</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120846287</v>
+        <v>120846276</v>
       </c>
       <c r="B24" t="n">
-        <v>91963</v>
+        <v>57367</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,13 +2959,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>784293</v>
+        <v>784412</v>
       </c>
       <c r="R24" t="n">
-        <v>7350235</v>
+        <v>7350117</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120846285</v>
+        <v>120846290</v>
       </c>
       <c r="B25" t="n">
-        <v>91991</v>
+        <v>91973</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3033,25 +3033,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>784260</v>
+        <v>784308</v>
       </c>
       <c r="R25" t="n">
-        <v>7350253</v>
+        <v>7350215</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>

--- a/artfynd/A 64127-2023 artfynd.xlsx
+++ b/artfynd/A 64127-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120846297</v>
+        <v>126284255</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsk, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>784426</v>
+        <v>784141</v>
       </c>
       <c r="R2" t="n">
-        <v>7350354</v>
+        <v>7350879</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,65 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120846281</v>
+        <v>126284254</v>
       </c>
       <c r="B3" t="n">
-        <v>91973</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsk, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784273</v>
+        <v>784260</v>
       </c>
       <c r="R3" t="n">
-        <v>7350210</v>
+        <v>7350797</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +837,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Väldigt många med blomställningar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,65 +862,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120846287</v>
+        <v>126284252</v>
       </c>
       <c r="B4" t="n">
-        <v>91973</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsk, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784293</v>
+        <v>784197</v>
       </c>
       <c r="R4" t="n">
-        <v>7350235</v>
+        <v>7350826</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +939,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>25 tal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120846275</v>
+        <v>126284265</v>
       </c>
       <c r="B5" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,37 +987,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4745</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsk, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784456</v>
+        <v>784092</v>
       </c>
       <c r="R5" t="n">
-        <v>7350102</v>
+        <v>7350943</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120846280</v>
+        <v>126284251</v>
       </c>
       <c r="B6" t="n">
-        <v>91973</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1084,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsk, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784294</v>
+        <v>784234</v>
       </c>
       <c r="R6" t="n">
-        <v>7350178</v>
+        <v>7350810</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1138,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,65 +1158,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120846279</v>
+        <v>126284264</v>
       </c>
       <c r="B7" t="n">
-        <v>91973</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsk, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784322</v>
+        <v>784231</v>
       </c>
       <c r="R7" t="n">
-        <v>7350175</v>
+        <v>7350785</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1235,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,65 +1255,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120846284</v>
+        <v>126284253</v>
       </c>
       <c r="B8" t="n">
-        <v>91973</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsk, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>784257</v>
+        <v>784217</v>
       </c>
       <c r="R8" t="n">
-        <v>7350260</v>
+        <v>7350810</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,12 +1332,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>8-10 rosetter +24 helt nära med blomställningar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,22 +1357,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120846244</v>
+        <v>120846297</v>
       </c>
       <c r="B9" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1385,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandträsket, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>784470</v>
+        <v>784426</v>
       </c>
       <c r="R9" t="n">
-        <v>7349932</v>
+        <v>7350354</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,15 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120846277</v>
+        <v>126284263</v>
       </c>
       <c r="B10" t="n">
-        <v>90717</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,37 +1482,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsk, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784361</v>
+        <v>784656</v>
       </c>
       <c r="R10" t="n">
-        <v>7350179</v>
+        <v>7350562</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1561,12 +1536,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,22 +1556,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120846292</v>
+        <v>120846281</v>
       </c>
       <c r="B11" t="n">
-        <v>91967</v>
+        <v>91973</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1580,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784322</v>
+        <v>784273</v>
       </c>
       <c r="R11" t="n">
-        <v>7350217</v>
+        <v>7350210</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1695,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120846272</v>
+        <v>120846287</v>
       </c>
       <c r="B12" t="n">
-        <v>98081</v>
+        <v>91973</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,38 +1682,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sandträsket, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784454</v>
+        <v>784293</v>
       </c>
       <c r="R12" t="n">
-        <v>7349938</v>
+        <v>7350235</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1797,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120846289</v>
+        <v>120846275</v>
       </c>
       <c r="B13" t="n">
-        <v>91985</v>
+        <v>91599</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1784,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>4745</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>784312</v>
+        <v>784456</v>
       </c>
       <c r="R13" t="n">
-        <v>7350223</v>
+        <v>7350102</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1899,7 +1874,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120846286</v>
+        <v>120846280</v>
       </c>
       <c r="B14" t="n">
         <v>91973</v>
@@ -1939,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>784290</v>
+        <v>784294</v>
       </c>
       <c r="R14" t="n">
-        <v>7350243</v>
+        <v>7350178</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2001,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120846285</v>
+        <v>120846279</v>
       </c>
       <c r="B15" t="n">
-        <v>92001</v>
+        <v>91973</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +1988,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>784260</v>
+        <v>784322</v>
       </c>
       <c r="R15" t="n">
-        <v>7350253</v>
+        <v>7350175</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2103,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120846242</v>
+        <v>120846284</v>
       </c>
       <c r="B16" t="n">
-        <v>91985</v>
+        <v>91973</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,34 +2094,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sandträsket, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>784572</v>
+        <v>784257</v>
       </c>
       <c r="R16" t="n">
-        <v>7349815</v>
+        <v>7350260</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2205,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120846243</v>
+        <v>120846244</v>
       </c>
       <c r="B17" t="n">
-        <v>98081</v>
+        <v>57504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2192,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>784480</v>
+        <v>784470</v>
       </c>
       <c r="R17" t="n">
-        <v>7349944</v>
+        <v>7349932</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2307,10 +2282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120846291</v>
+        <v>120846277</v>
       </c>
       <c r="B18" t="n">
-        <v>91965</v>
+        <v>90717</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>784307</v>
+        <v>784361</v>
       </c>
       <c r="R18" t="n">
-        <v>7350222</v>
+        <v>7350179</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2409,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120846283</v>
+        <v>120846292</v>
       </c>
       <c r="B19" t="n">
-        <v>91973</v>
+        <v>91967</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2396,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2424,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>784262</v>
+        <v>784322</v>
       </c>
       <c r="R19" t="n">
-        <v>7350259</v>
+        <v>7350217</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2511,10 +2486,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120846282</v>
+        <v>120846272</v>
       </c>
       <c r="B20" t="n">
-        <v>92001</v>
+        <v>98081</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,38 +2498,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsket, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>784268</v>
+        <v>784454</v>
       </c>
       <c r="R20" t="n">
-        <v>7350210</v>
+        <v>7349938</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2613,7 +2588,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120846241</v>
+        <v>120846289</v>
       </c>
       <c r="B21" t="n">
         <v>91985</v>
@@ -2649,14 +2624,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sandträsket, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>784627</v>
+        <v>784312</v>
       </c>
       <c r="R21" t="n">
-        <v>7349780</v>
+        <v>7350223</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2715,7 +2690,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120846293</v>
+        <v>120846286</v>
       </c>
       <c r="B22" t="n">
         <v>91973</v>
@@ -2755,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>784365</v>
+        <v>784290</v>
       </c>
       <c r="R22" t="n">
-        <v>7350253</v>
+        <v>7350243</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2817,10 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120846288</v>
+        <v>120846285</v>
       </c>
       <c r="B23" t="n">
-        <v>91967</v>
+        <v>92001</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2808,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2832,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>784286</v>
+        <v>784260</v>
       </c>
       <c r="R23" t="n">
-        <v>7350227</v>
+        <v>7350253</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2919,10 +2894,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120846276</v>
+        <v>120846242</v>
       </c>
       <c r="B24" t="n">
-        <v>57367</v>
+        <v>91985</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2931,41 +2906,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsket, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>784412</v>
+        <v>784572</v>
       </c>
       <c r="R24" t="n">
-        <v>7350117</v>
+        <v>7349815</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3021,10 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120846290</v>
+        <v>120846243</v>
       </c>
       <c r="B25" t="n">
-        <v>91973</v>
+        <v>98081</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3033,38 +3008,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Sandträsket, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>784308</v>
+        <v>784480</v>
       </c>
       <c r="R25" t="n">
-        <v>7350215</v>
+        <v>7349944</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3120,6 +3095,1730 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120846291</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91965</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>784307</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7350222</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120846283</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91973</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>784262</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7350259</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120846282</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92001</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>784268</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7350210</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120846241</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91985</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sandträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>784627</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7349780</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120846293</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91973</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>784365</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7350253</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120846288</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91967</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>784286</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7350227</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120846276</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>784412</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7350117</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120846290</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91973</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>784308</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7350215</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126284258</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sandträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>784337</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7350108</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>15tal</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126284266</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sandträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>784686</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7349972</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126284256</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sandträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>784369</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7350111</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>25 +15 rosetter  tre blomställningar</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126284259</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sandträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>784521</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7349985</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>5 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126284257</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sandträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>784377</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7350105</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>8 rosetter</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126284267</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92528</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sandträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>784414</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7350157</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126284262</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sandträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>784466</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7349966</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>4 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126284261</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sandträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>784519</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7349967</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>15 tal bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126284260</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sandträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>784524</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7349959</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>13 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64127-2023 artfynd.xlsx
+++ b/artfynd/A 64127-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126284255</v>
       </c>
       <c r="B2" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126284254</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126284252</v>
+        <v>126284265</v>
       </c>
       <c r="B4" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784197</v>
+        <v>784092</v>
       </c>
       <c r="R4" t="n">
-        <v>7350826</v>
+        <v>7350943</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>25 tal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126284265</v>
+        <v>126284252</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784092</v>
+        <v>784197</v>
       </c>
       <c r="R5" t="n">
-        <v>7350943</v>
+        <v>7350826</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>25 tal</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,7 +1076,7 @@
         <v>126284251</v>
       </c>
       <c r="B6" t="n">
-        <v>57756</v>
+        <v>57760</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>126284264</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>126284253</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>126284263</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>126284258</v>
       </c>
       <c r="B34" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>126284266</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>126284256</v>
       </c>
       <c r="B36" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>126284259</v>
       </c>
       <c r="B37" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>126284257</v>
       </c>
       <c r="B38" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>126284267</v>
       </c>
       <c r="B39" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>126284262</v>
       </c>
       <c r="B40" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>126284261</v>
       </c>
       <c r="B41" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>126284260</v>
       </c>
       <c r="B42" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 64127-2023 artfynd.xlsx
+++ b/artfynd/A 64127-2023 artfynd.xlsx
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126284265</v>
+        <v>126284252</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>98349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784092</v>
+        <v>784197</v>
       </c>
       <c r="R4" t="n">
-        <v>7350943</v>
+        <v>7350826</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>25 tal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126284252</v>
+        <v>126284265</v>
       </c>
       <c r="B5" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784197</v>
+        <v>784092</v>
       </c>
       <c r="R5" t="n">
-        <v>7350826</v>
+        <v>7350943</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>25 tal</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 64127-2023 artfynd.xlsx
+++ b/artfynd/A 64127-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>126284255</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126284254</v>
       </c>
       <c r="B3" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126284252</v>
+        <v>126284265</v>
       </c>
       <c r="B4" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784197</v>
+        <v>784092</v>
       </c>
       <c r="R4" t="n">
-        <v>7350826</v>
+        <v>7350943</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>25 tal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126284265</v>
+        <v>126284252</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784092</v>
+        <v>784197</v>
       </c>
       <c r="R5" t="n">
-        <v>7350943</v>
+        <v>7350826</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>25 tal</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1270,7 +1270,7 @@
         <v>126284253</v>
       </c>
       <c r="B8" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>126284258</v>
       </c>
       <c r="B34" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>126284256</v>
       </c>
       <c r="B36" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>126284259</v>
       </c>
       <c r="B37" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>126284257</v>
       </c>
       <c r="B38" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>126284262</v>
       </c>
       <c r="B40" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>126284261</v>
       </c>
       <c r="B41" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>126284260</v>
       </c>
       <c r="B42" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4819,6 +4819,2285 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126380925</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>784410</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7349970</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126380919</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>784341</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7350108</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126380935</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>784683</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7349798</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126380922</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>784350</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7350038</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126380923</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>784373</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7350015</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126380930</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>784469</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7349942</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126380920</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>784332</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7350094</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126380932</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>784515</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7349962</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126380934</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>784514</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7350048</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126381207</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98269</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>784369</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7350109</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126380924</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>784377</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7350011</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126380926</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>784408</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7349964</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126381211</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98269</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>784336</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7350140</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126380927</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>784455</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7349924</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126380933</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>784515</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7350041</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126380928</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>784450</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7349934</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126380929</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>784458</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7349938</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126381208</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98373</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>784331</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7350097</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126381210</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98373</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>784340</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7350119</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126380916</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>784338</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7350142</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126380918</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>784340</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7350120</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126380917</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>784355</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7350119</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126380921</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Flakaberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>784344</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7350056</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Johan Kristoffersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64127-2023 artfynd.xlsx
+++ b/artfynd/A 64127-2023 artfynd.xlsx
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126284265</v>
+        <v>126284252</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784092</v>
+        <v>784197</v>
       </c>
       <c r="R4" t="n">
-        <v>7350943</v>
+        <v>7350826</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>25 tal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126284252</v>
+        <v>126284265</v>
       </c>
       <c r="B5" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784197</v>
+        <v>784092</v>
       </c>
       <c r="R5" t="n">
-        <v>7350826</v>
+        <v>7350943</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>25 tal</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -4822,7 +4822,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126380925</v>
+        <v>126380919</v>
       </c>
       <c r="B43" t="n">
         <v>98352</v>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>784410</v>
+        <v>784341</v>
       </c>
       <c r="R43" t="n">
-        <v>7349970</v>
+        <v>7350108</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4919,7 +4919,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126380919</v>
+        <v>126380935</v>
       </c>
       <c r="B44" t="n">
         <v>98352</v>
@@ -4947,17 +4947,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>784341</v>
+        <v>784683</v>
       </c>
       <c r="R44" t="n">
-        <v>7350108</v>
+        <v>7349798</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5016,7 +5020,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126380935</v>
+        <v>126380925</v>
       </c>
       <c r="B45" t="n">
         <v>98352</v>
@@ -5044,21 +5048,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>784683</v>
+        <v>784410</v>
       </c>
       <c r="R45" t="n">
-        <v>7349798</v>
+        <v>7349970</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5214,7 +5214,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126380923</v>
+        <v>126380930</v>
       </c>
       <c r="B47" t="n">
         <v>98352</v>
@@ -5242,17 +5242,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>784373</v>
+        <v>784469</v>
       </c>
       <c r="R47" t="n">
-        <v>7350015</v>
+        <v>7349942</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5311,7 +5315,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126380930</v>
+        <v>126380920</v>
       </c>
       <c r="B48" t="n">
         <v>98352</v>
@@ -5339,21 +5343,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>784469</v>
+        <v>784332</v>
       </c>
       <c r="R48" t="n">
-        <v>7349942</v>
+        <v>7350094</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5412,7 +5412,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126380920</v>
+        <v>126380923</v>
       </c>
       <c r="B49" t="n">
         <v>98352</v>
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>784332</v>
+        <v>784373</v>
       </c>
       <c r="R49" t="n">
-        <v>7350094</v>
+        <v>7350015</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5509,7 +5509,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126380932</v>
+        <v>126380934</v>
       </c>
       <c r="B50" t="n">
         <v>98352</v>
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>784515</v>
+        <v>784514</v>
       </c>
       <c r="R50" t="n">
-        <v>7349962</v>
+        <v>7350048</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126380934</v>
+        <v>126380932</v>
       </c>
       <c r="B51" t="n">
         <v>98352</v>
@@ -5649,10 +5649,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>784514</v>
+        <v>784515</v>
       </c>
       <c r="R51" t="n">
-        <v>7350048</v>
+        <v>7349962</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5711,49 +5711,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126381207</v>
+        <v>126380924</v>
       </c>
       <c r="B52" t="n">
-        <v>98269</v>
+        <v>98352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>784369</v>
+        <v>784377</v>
       </c>
       <c r="R52" t="n">
-        <v>7350109</v>
+        <v>7350011</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5812,45 +5808,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126380924</v>
+        <v>126381207</v>
       </c>
       <c r="B53" t="n">
-        <v>98352</v>
+        <v>98269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>784377</v>
+        <v>784369</v>
       </c>
       <c r="R53" t="n">
-        <v>7350011</v>
+        <v>7350109</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6006,32 +6006,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126381211</v>
+        <v>126380933</v>
       </c>
       <c r="B55" t="n">
-        <v>98269</v>
+        <v>98352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>784336</v>
+        <v>784515</v>
       </c>
       <c r="R55" t="n">
-        <v>7350140</v>
+        <v>7350041</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6208,32 +6208,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126380933</v>
+        <v>126381211</v>
       </c>
       <c r="B57" t="n">
-        <v>98352</v>
+        <v>98269</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>784515</v>
+        <v>784336</v>
       </c>
       <c r="R57" t="n">
-        <v>7350041</v>
+        <v>7350140</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>

--- a/artfynd/A 64127-2023 artfynd.xlsx
+++ b/artfynd/A 64127-2023 artfynd.xlsx
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126284264</v>
+        <v>126284253</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784231</v>
+        <v>784217</v>
       </c>
       <c r="R7" t="n">
-        <v>7350785</v>
+        <v>7350810</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1241,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>8-10 rosetter +24 helt nära med blomställningar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126284253</v>
+        <v>126284264</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>784217</v>
+        <v>784231</v>
       </c>
       <c r="R8" t="n">
-        <v>7350810</v>
+        <v>7350785</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1338,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>8-10 rosetter +24 helt nära med blomställningar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -6410,32 +6410,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126380929</v>
+        <v>126381208</v>
       </c>
       <c r="B59" t="n">
-        <v>98352</v>
+        <v>98373</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>784458</v>
+        <v>784331</v>
       </c>
       <c r="R59" t="n">
-        <v>7349938</v>
+        <v>7350097</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6511,7 +6511,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126381208</v>
+        <v>126381210</v>
       </c>
       <c r="B60" t="n">
         <v>98373</v>
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>784331</v>
+        <v>784340</v>
       </c>
       <c r="R60" t="n">
-        <v>7350097</v>
+        <v>7350119</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6612,32 +6612,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126381210</v>
+        <v>126380929</v>
       </c>
       <c r="B61" t="n">
-        <v>98373</v>
+        <v>98352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>784340</v>
+        <v>784458</v>
       </c>
       <c r="R61" t="n">
-        <v>7350119</v>
+        <v>7349938</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 64127-2023 artfynd.xlsx
+++ b/artfynd/A 64127-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126284255</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126284254</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>126284252</v>
       </c>
       <c r="B4" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126284265</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>126284251</v>
       </c>
       <c r="B6" t="n">
-        <v>57760</v>
+        <v>57761</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>126284253</v>
       </c>
       <c r="B7" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>126284264</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>126284263</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>126284258</v>
       </c>
       <c r="B34" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>126284266</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>126284256</v>
       </c>
       <c r="B36" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>126284259</v>
       </c>
       <c r="B37" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>126284257</v>
       </c>
       <c r="B38" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>126284267</v>
       </c>
       <c r="B39" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>126284262</v>
       </c>
       <c r="B40" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>126284261</v>
       </c>
       <c r="B41" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>126284260</v>
       </c>
       <c r="B42" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>126380919</v>
       </c>
       <c r="B43" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4919,10 +4919,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126380935</v>
+        <v>126380925</v>
       </c>
       <c r="B44" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4947,21 +4947,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>784683</v>
+        <v>784410</v>
       </c>
       <c r="R44" t="n">
-        <v>7349798</v>
+        <v>7349970</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5020,10 +5016,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126380925</v>
+        <v>126380935</v>
       </c>
       <c r="B45" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5048,17 +5044,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>784410</v>
+        <v>784683</v>
       </c>
       <c r="R45" t="n">
-        <v>7349970</v>
+        <v>7349798</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5120,7 +5120,7 @@
         <v>126380922</v>
       </c>
       <c r="B46" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5214,10 +5214,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126380930</v>
+        <v>126380923</v>
       </c>
       <c r="B47" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5242,21 +5242,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>784469</v>
+        <v>784373</v>
       </c>
       <c r="R47" t="n">
-        <v>7349942</v>
+        <v>7350015</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5315,10 +5311,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126380920</v>
+        <v>126380930</v>
       </c>
       <c r="B48" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5343,17 +5339,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>784332</v>
+        <v>784469</v>
       </c>
       <c r="R48" t="n">
-        <v>7350094</v>
+        <v>7349942</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5412,10 +5412,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126380923</v>
+        <v>126380920</v>
       </c>
       <c r="B49" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>784373</v>
+        <v>784332</v>
       </c>
       <c r="R49" t="n">
-        <v>7350015</v>
+        <v>7350094</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5509,10 +5509,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126380934</v>
+        <v>126380932</v>
       </c>
       <c r="B50" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>784514</v>
+        <v>784515</v>
       </c>
       <c r="R50" t="n">
-        <v>7350048</v>
+        <v>7349962</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5610,10 +5610,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126380932</v>
+        <v>126380934</v>
       </c>
       <c r="B51" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5649,10 +5649,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>784515</v>
+        <v>784514</v>
       </c>
       <c r="R51" t="n">
-        <v>7349962</v>
+        <v>7350048</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5711,45 +5711,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126380924</v>
+        <v>126381207</v>
       </c>
       <c r="B52" t="n">
-        <v>98352</v>
+        <v>98278</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>784377</v>
+        <v>784369</v>
       </c>
       <c r="R52" t="n">
-        <v>7350011</v>
+        <v>7350109</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5808,49 +5812,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126381207</v>
+        <v>126380924</v>
       </c>
       <c r="B53" t="n">
-        <v>98269</v>
+        <v>98361</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>784369</v>
+        <v>784377</v>
       </c>
       <c r="R53" t="n">
-        <v>7350109</v>
+        <v>7350011</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5912,7 +5912,7 @@
         <v>126380926</v>
       </c>
       <c r="B54" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6006,32 +6006,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126380933</v>
+        <v>126381211</v>
       </c>
       <c r="B55" t="n">
-        <v>98352</v>
+        <v>98278</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>784515</v>
+        <v>784336</v>
       </c>
       <c r="R55" t="n">
-        <v>7350041</v>
+        <v>7350140</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6107,10 +6107,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126380927</v>
+        <v>126380933</v>
       </c>
       <c r="B56" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>784455</v>
+        <v>784515</v>
       </c>
       <c r="R56" t="n">
-        <v>7349924</v>
+        <v>7350041</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6208,37 +6208,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126381211</v>
+        <v>126380927</v>
       </c>
       <c r="B57" t="n">
-        <v>98269</v>
+        <v>98361</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>784336</v>
+        <v>784455</v>
       </c>
       <c r="R57" t="n">
-        <v>7350140</v>
+        <v>7349924</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6312,7 +6312,7 @@
         <v>126380928</v>
       </c>
       <c r="B58" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6410,32 +6410,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126381208</v>
+        <v>126380929</v>
       </c>
       <c r="B59" t="n">
-        <v>98373</v>
+        <v>98361</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>784331</v>
+        <v>784458</v>
       </c>
       <c r="R59" t="n">
-        <v>7350097</v>
+        <v>7349938</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126381210</v>
+        <v>126381208</v>
       </c>
       <c r="B60" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>784340</v>
+        <v>784331</v>
       </c>
       <c r="R60" t="n">
-        <v>7350119</v>
+        <v>7350097</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6612,32 +6612,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126380929</v>
+        <v>126381210</v>
       </c>
       <c r="B61" t="n">
-        <v>98352</v>
+        <v>98382</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>784458</v>
+        <v>784340</v>
       </c>
       <c r="R61" t="n">
-        <v>7349938</v>
+        <v>7350119</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6716,7 +6716,7 @@
         <v>126380916</v>
       </c>
       <c r="B62" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>126380918</v>
       </c>
       <c r="B63" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>126380917</v>
       </c>
       <c r="B64" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>126380921</v>
       </c>
       <c r="B65" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 64127-2023 artfynd.xlsx
+++ b/artfynd/A 64127-2023 artfynd.xlsx
@@ -6107,7 +6107,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126380933</v>
+        <v>126380927</v>
       </c>
       <c r="B56" t="n">
         <v>98361</v>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>784515</v>
+        <v>784455</v>
       </c>
       <c r="R56" t="n">
-        <v>7350041</v>
+        <v>7349924</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6208,7 +6208,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126380927</v>
+        <v>126380933</v>
       </c>
       <c r="B57" t="n">
         <v>98361</v>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>784455</v>
+        <v>784515</v>
       </c>
       <c r="R57" t="n">
-        <v>7349924</v>
+        <v>7350041</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>

--- a/artfynd/A 64127-2023 artfynd.xlsx
+++ b/artfynd/A 64127-2023 artfynd.xlsx
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126284252</v>
+        <v>126284265</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784197</v>
+        <v>784092</v>
       </c>
       <c r="R4" t="n">
-        <v>7350826</v>
+        <v>7350943</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>25 tal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126284265</v>
+        <v>126284252</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784092</v>
+        <v>784197</v>
       </c>
       <c r="R5" t="n">
-        <v>7350943</v>
+        <v>7350826</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>25 tal</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126284253</v>
+        <v>126284264</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784217</v>
+        <v>784231</v>
       </c>
       <c r="R7" t="n">
-        <v>7350810</v>
+        <v>7350785</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1241,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>8-10 rosetter +24 helt nära med blomställningar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126284264</v>
+        <v>126284253</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>784231</v>
+        <v>784217</v>
       </c>
       <c r="R8" t="n">
-        <v>7350785</v>
+        <v>7350810</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1343,6 +1338,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>8-10 rosetter +24 helt nära med blomställningar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -4822,7 +4822,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126380919</v>
+        <v>126380925</v>
       </c>
       <c r="B43" t="n">
         <v>98361</v>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>784341</v>
+        <v>784410</v>
       </c>
       <c r="R43" t="n">
-        <v>7350108</v>
+        <v>7349970</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4919,7 +4919,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126380925</v>
+        <v>126380919</v>
       </c>
       <c r="B44" t="n">
         <v>98361</v>
@@ -4954,10 +4954,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>784410</v>
+        <v>784341</v>
       </c>
       <c r="R44" t="n">
-        <v>7349970</v>
+        <v>7350108</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5711,49 +5711,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126381207</v>
+        <v>126380924</v>
       </c>
       <c r="B52" t="n">
-        <v>98278</v>
+        <v>98361</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>784369</v>
+        <v>784377</v>
       </c>
       <c r="R52" t="n">
-        <v>7350109</v>
+        <v>7350011</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5812,45 +5808,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126380924</v>
+        <v>126381207</v>
       </c>
       <c r="B53" t="n">
-        <v>98361</v>
+        <v>98278</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>784377</v>
+        <v>784369</v>
       </c>
       <c r="R53" t="n">
-        <v>7350011</v>
+        <v>7350109</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6006,37 +6006,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126381211</v>
+        <v>126380927</v>
       </c>
       <c r="B55" t="n">
-        <v>98278</v>
+        <v>98361</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>784336</v>
+        <v>784455</v>
       </c>
       <c r="R55" t="n">
-        <v>7350140</v>
+        <v>7349924</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6107,7 +6107,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126380927</v>
+        <v>126380933</v>
       </c>
       <c r="B56" t="n">
         <v>98361</v>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>784455</v>
+        <v>784515</v>
       </c>
       <c r="R56" t="n">
-        <v>7349924</v>
+        <v>7350041</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6208,32 +6208,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126380933</v>
+        <v>126381211</v>
       </c>
       <c r="B57" t="n">
-        <v>98361</v>
+        <v>98278</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>784515</v>
+        <v>784336</v>
       </c>
       <c r="R57" t="n">
-        <v>7350041</v>
+        <v>7350140</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>

--- a/artfynd/A 64127-2023 artfynd.xlsx
+++ b/artfynd/A 64127-2023 artfynd.xlsx
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126284265</v>
+        <v>126284252</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784092</v>
+        <v>784197</v>
       </c>
       <c r="R4" t="n">
-        <v>7350943</v>
+        <v>7350826</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>25 tal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126284252</v>
+        <v>126284265</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784197</v>
+        <v>784092</v>
       </c>
       <c r="R5" t="n">
-        <v>7350826</v>
+        <v>7350943</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>25 tal</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -6006,37 +6006,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126380927</v>
+        <v>126381211</v>
       </c>
       <c r="B55" t="n">
-        <v>98361</v>
+        <v>98278</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>784455</v>
+        <v>784336</v>
       </c>
       <c r="R55" t="n">
-        <v>7349924</v>
+        <v>7350140</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6107,7 +6107,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126380933</v>
+        <v>126380927</v>
       </c>
       <c r="B56" t="n">
         <v>98361</v>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>784515</v>
+        <v>784455</v>
       </c>
       <c r="R56" t="n">
-        <v>7350041</v>
+        <v>7349924</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6208,32 +6208,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126381211</v>
+        <v>126380933</v>
       </c>
       <c r="B57" t="n">
-        <v>98278</v>
+        <v>98361</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>784336</v>
+        <v>784515</v>
       </c>
       <c r="R57" t="n">
-        <v>7350140</v>
+        <v>7350041</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>

--- a/artfynd/A 64127-2023 artfynd.xlsx
+++ b/artfynd/A 64127-2023 artfynd.xlsx
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126284264</v>
+        <v>126284253</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784231</v>
+        <v>784217</v>
       </c>
       <c r="R7" t="n">
-        <v>7350785</v>
+        <v>7350810</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1241,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>8-10 rosetter +24 helt nära med blomställningar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126284253</v>
+        <v>126284264</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>784217</v>
+        <v>784231</v>
       </c>
       <c r="R8" t="n">
-        <v>7350810</v>
+        <v>7350785</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1338,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>8-10 rosetter +24 helt nära med blomställningar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -6006,37 +6006,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126381211</v>
+        <v>126380927</v>
       </c>
       <c r="B55" t="n">
-        <v>98278</v>
+        <v>98361</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>784336</v>
+        <v>784455</v>
       </c>
       <c r="R55" t="n">
-        <v>7350140</v>
+        <v>7349924</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6107,7 +6107,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126380927</v>
+        <v>126380933</v>
       </c>
       <c r="B56" t="n">
         <v>98361</v>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>784455</v>
+        <v>784515</v>
       </c>
       <c r="R56" t="n">
-        <v>7349924</v>
+        <v>7350041</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6208,32 +6208,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126380933</v>
+        <v>126381211</v>
       </c>
       <c r="B57" t="n">
-        <v>98361</v>
+        <v>98278</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>784515</v>
+        <v>784336</v>
       </c>
       <c r="R57" t="n">
-        <v>7350041</v>
+        <v>7350140</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
